--- a/dimensionless.xlsx
+++ b/dimensionless.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38865A22-0B97-4F1A-97EB-32B16EE0EC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7455" tabRatio="793"/>
   </bookViews>
   <sheets>
     <sheet name="Table 7-1" sheetId="1" r:id="rId1"/>
@@ -23,12 +22,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Dimensionless w.r.t. k</t>
-  </si>
-  <si>
-    <t>Dimensionless w.r.t. d</t>
-  </si>
-  <si>
     <t>Water depth</t>
   </si>
   <si>
@@ -101,7 +94,7 @@
     <t>Ū/√(gd)</t>
   </si>
   <si>
-    <t>Wave volume flux, q = Ū d − Q</t>
+    <t>Wave volume flux, q = Ūd − Q</t>
   </si>
   <si>
     <t>q√(k³/g)</t>
@@ -149,7 +142,7 @@
     <t>Impulse</t>
   </si>
   <si>
-    <t>I√k³/(ρ√g)</t>
+    <t>I√(k³)/(ρ√g)</t>
   </si>
   <si>
     <t>I/(ρ√(gd³))</t>
@@ -176,71 +169,93 @@
     <t>Mean square of bed velocity</t>
   </si>
   <si>
-    <t>u_b²k/g</t>
-  </si>
-  <si>
-    <t>u_b²/gd</t>
+    <t>uᵦ²k/g</t>
+  </si>
+  <si>
+    <t>uᵦ²/gd</t>
   </si>
   <si>
     <t>Radiation stress</t>
   </si>
   <si>
-    <t>S_xx k²/ρg</t>
-  </si>
-  <si>
-    <t>S_xx/ρgd²</t>
+    <t>Sₓₓk²/ρg</t>
+  </si>
+  <si>
+    <t>Sₓₓ/ρgd²</t>
   </si>
   <si>
     <t>Wave power</t>
   </si>
   <si>
-    <t>Fk^(5/2)/(ρ g^(3/2))</t>
-  </si>
-  <si>
-    <t>F/(ρ g^(3/2) d^(5/2))</t>
+    <t>Fk⁵⁄²/(ρg³⁄²)</t>
+  </si>
+  <si>
+    <t>F/(ρg³⁄²d⁵⁄²)</t>
   </si>
   <si>
     <t>Fourier coefficients (dimensionless)</t>
   </si>
   <si>
-    <t>B_j</t>
-  </si>
-  <si>
-    <t>E_j</t>
-  </si>
-  <si>
-    <t>B_1</t>
-  </si>
-  <si>
-    <t>E_1</t>
+    <t>Bⱼ</t>
+  </si>
+  <si>
+    <t>Eⱼ</t>
+  </si>
+  <si>
+    <t>B₁</t>
+  </si>
+  <si>
+    <t>E₁</t>
   </si>
   <si>
     <t>…</t>
   </si>
   <si>
-    <t>B_N</t>
-  </si>
-  <si>
-    <t>E_N</t>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+  </si>
+  <si>
+    <t>Dimensionless to k</t>
+  </si>
+  <si>
+    <t>Dimensionless to d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -250,11 +265,39 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,12 +306,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="65"/>
-        <bgColor auto="1"/>
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -339,91 +386,47 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9AA0A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9AA0A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9AA0A6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="6">
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF9AA0A6"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9AA0A6"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9AA0A6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9AA0A6"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF9AA0A6"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF9AA0A6"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -431,38 +434,8 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF9AA0A6"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9AA0A6"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9AA0A6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9AA0A6"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF9AA0A6"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF9AA0A6"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -470,36 +443,8 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF9AA0A6"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9AA0A6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9AA0A6"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF9AA0A6"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF9AA0A6"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -507,50 +452,8 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF9AA0A6"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9AA0A6"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color rgb="FF9AA0A6"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF9AA0A6"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FF4F4F4F"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF4F4F4F"/>
-        </right>
-        <top style="medium">
-          <color rgb="FF4F4F4F"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF4F4F4F"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -558,69 +461,20 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF9AA0A6"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF9AA0A6"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9AA0A6"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color rgb="FF9AA0A6"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF9AA0A6"/>
-        </horizontal>
-      </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -633,18 +487,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table7_1" displayName="Table7_1" ref="A3:C26" headerRowDxfId="7" dataDxfId="5" totalsRowDxfId="3" headerRowBorderDxfId="6" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table7_1" displayName="Table7_1" ref="A3:C26" headerRowDxfId="5" dataDxfId="4" totalsRowDxfId="3">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Quantity" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Dimensionless w.r.t. k" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dimensionless w.r.t. d" dataDxfId="0"/>
+    <tableColumn id="1" name="Quantity" dataDxfId="2"/>
+    <tableColumn id="2" name="Dimensionless to k" dataDxfId="1"/>
+    <tableColumn id="3" name="Dimensionless to d" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -686,72 +540,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -759,55 +555,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -816,13 +572,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -856,24 +612,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -899,7 +644,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -927,281 +672,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.21875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="38" style="1" customWidth="1"/>
+    <col min="2" max="3" width="26" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="B16" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="B18" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="B20" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="B21" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="B22" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B23" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="2" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="2" t="s">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7"/>
+      <c r="B26" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1209,8 +956,8 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="120" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>

--- a/dimensionless.xlsx
+++ b/dimensionless.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3228AA-AC3A-4F59-BAB6-665AF8272142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7455" tabRatio="793"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 7-1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Table 7-1. Quantities printed out at the head of file SOLUTION.RES</t>
   </si>
@@ -200,45 +201,6 @@
   </si>
   <si>
     <t>Eⱼ</t>
-  </si>
-  <si>
-    <t>B₁</t>
-  </si>
-  <si>
-    <t>E₁</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <r>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
   </si>
   <si>
     <t>Dimensionless to k</t>
@@ -250,8 +212,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,20 +232,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -293,6 +241,12 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -311,11 +265,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -324,64 +279,112 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FF9AA0A6"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF9AA0A6"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF9AA0A6"/>
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -390,43 +393,76 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -436,6 +472,22 @@
         <u val="none"/>
         <sz val="12"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -445,6 +497,24 @@
         <u val="none"/>
         <sz val="12"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -454,6 +524,26 @@
         <u val="none"/>
         <sz val="12"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -463,6 +553,47 @@
         <u val="none"/>
         <sz val="12"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="medium">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -487,11 +618,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table7_1" displayName="Table7_1" ref="A3:C26" headerRowDxfId="5" dataDxfId="4" totalsRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table7_1" displayName="Table7_1" ref="A3:C23" headerRowDxfId="0" dataDxfId="7" totalsRowDxfId="1" headerRowBorderDxfId="5" tableBorderDxfId="6">
   <tableColumns count="3">
-    <tableColumn id="1" name="Quantity" dataDxfId="2"/>
-    <tableColumn id="2" name="Dimensionless to k" dataDxfId="1"/>
-    <tableColumn id="3" name="Dimensionless to d" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Quantity" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Dimensionless to k" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dimensionless to d" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -672,283 +803,256 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
